--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_36.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1859182.113950345</v>
+        <v>1851285.663886918</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747601</v>
+        <v>7154817.030747597</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747601</v>
+        <v>7154817.030747597</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097732</v>
+        <v>1421810.501097731</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097732</v>
+        <v>1421810.501097731</v>
       </c>
     </row>
     <row r="11">
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>26.7387362314949</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -784,10 +784,10 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>385</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>371.5681244750684</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -857,7 +857,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>324.2480957795422</v>
+        <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
         <v>326.6021279811511</v>
@@ -909,10 +909,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I5" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>385</v>
+        <v>333.9365645502421</v>
       </c>
       <c r="S9" t="n">
         <v>385</v>
@@ -1267,10 +1267,10 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>142.9948237414541</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>275.3413603594427</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1559,19 +1559,19 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>229.9677708001137</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D14" t="n">
         <v>185.3391557398498</v>
@@ -1623,7 +1623,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1805,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R16" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>25.87859882829446</v>
+        <v>31.37179138541422</v>
       </c>
       <c r="S17" t="n">
         <v>269.8481678023229</v>
@@ -2364,7 +2364,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S23" t="n">
-        <v>269.8481678023229</v>
+        <v>275.3413603594427</v>
       </c>
       <c r="T23" t="n">
         <v>361.6755817285639</v>
@@ -2379,7 +2379,7 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>372.7750260177875</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y23" t="n">
         <v>286.3174326828064</v>
@@ -2571,7 +2571,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>291.8106252399262</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2753,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>184.8564821639885</v>
       </c>
       <c r="F29" t="n">
         <v>179.8896287080119</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
         <v>269.8481678023229</v>
@@ -2987,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U32" t="n">
-        <v>424.2212965486107</v>
+        <v>429.7144891057306</v>
       </c>
       <c r="V32" t="n">
         <v>404.8510241668239</v>
@@ -3182,22 +3182,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.572420793687971</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>3.77112610161862</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3276,7 +3276,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
@@ -3318,7 +3318,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U35" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V35" t="n">
         <v>279.8510241668239</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>91.60958778454074</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3358,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
-        <v>250.9091418516077</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
         <v>50.21035976018675</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3586,10 +3586,10 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3637,7 +3637,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W39" t="n">
         <v>82.37314290982852</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3978,7 +3978,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D44" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E44" t="n">
         <v>54.36328960686865</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97.23431917176916</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4102,10 +4102,10 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U45" t="n">
         <v>50.21035976018675</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
         <v>30.8</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E3" t="n">
-        <v>30.8</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G3" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H3" t="n">
         <v>30.8</v>
@@ -4427,25 +4427,25 @@
         <v>862.6434684666581</v>
       </c>
       <c r="S3" t="n">
-        <v>473.7545795777692</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>98.43324172416462</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>98.22075711791538</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>83.56351753052128</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W3" t="n">
-        <v>50.86337317715914</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>398.4937896098788</v>
+        <v>785.9773458299743</v>
       </c>
       <c r="C4" t="n">
-        <v>524.4957954283146</v>
+        <v>911.9793516484101</v>
       </c>
       <c r="D4" t="n">
-        <v>524.4957954283146</v>
+        <v>911.9793516484101</v>
       </c>
       <c r="E4" t="n">
-        <v>524.4957954283146</v>
+        <v>1029.808255859823</v>
       </c>
       <c r="F4" t="n">
-        <v>524.4957954283146</v>
+        <v>1029.808255859823</v>
       </c>
       <c r="G4" t="n">
-        <v>677.9023613151999</v>
+        <v>1183.214821746708</v>
       </c>
       <c r="H4" t="n">
-        <v>847.4189464745974</v>
+        <v>1352.731406906106</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1352.731406906106</v>
       </c>
       <c r="J4" t="n">
         <v>1429.635566063132</v>
@@ -4485,19 +4485,19 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q4" t="n">
         <v>360.7011393749001</v>
@@ -4506,25 +4506,25 @@
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>115.1935706711692</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V4" t="n">
-        <v>115.1935706711692</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="W4" t="n">
-        <v>287.0844889308466</v>
+        <v>674.568045150942</v>
       </c>
       <c r="X4" t="n">
-        <v>287.0844889308466</v>
+        <v>674.568045150942</v>
       </c>
       <c r="Y4" t="n">
-        <v>398.4937896098788</v>
+        <v>785.9773458299743</v>
       </c>
     </row>
     <row r="5">
@@ -4552,7 +4552,7 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
@@ -4692,16 +4692,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>398.4937896098788</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="C7" t="n">
-        <v>524.4957954283146</v>
+        <v>403.3531984567225</v>
       </c>
       <c r="D7" t="n">
-        <v>524.4957954283146</v>
+        <v>403.3531984567225</v>
       </c>
       <c r="E7" t="n">
-        <v>524.4957954283146</v>
+        <v>403.3531984567225</v>
       </c>
       <c r="F7" t="n">
         <v>524.4957954283146</v>
@@ -4722,46 +4722,46 @@
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>151.9425969715922</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>398.4937896098788</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V7" t="n">
-        <v>398.4937896098788</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="W7" t="n">
-        <v>398.4937896098788</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="X7" t="n">
-        <v>398.4937896098788</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="Y7" t="n">
-        <v>398.4937896098788</v>
+        <v>277.3511926382866</v>
       </c>
     </row>
     <row r="8">
@@ -4771,40 +4771,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G8" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="L8" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="M8" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="N8" t="n">
         <v>396.55</v>
@@ -4822,25 +4822,25 @@
         <v>1540</v>
       </c>
       <c r="S8" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T8" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V8" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4895,22 +4895,22 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>622.5159909842129</v>
+        <v>848.922759206675</v>
       </c>
       <c r="S9" t="n">
-        <v>233.6271020953239</v>
+        <v>460.0338703177861</v>
       </c>
       <c r="T9" t="n">
-        <v>228.2152180372292</v>
+        <v>454.6219862596914</v>
       </c>
       <c r="U9" t="n">
-        <v>228.00273343098</v>
+        <v>454.4095016534421</v>
       </c>
       <c r="V9" t="n">
-        <v>83.56351753052128</v>
+        <v>439.752262066048</v>
       </c>
       <c r="W9" t="n">
         <v>50.86337317715914</v>
@@ -4929,19 +4929,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1024.420229061081</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="C10" t="n">
-        <v>1024.420229061081</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="D10" t="n">
-        <v>1024.420229061081</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="E10" t="n">
-        <v>1024.420229061081</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="F10" t="n">
-        <v>1024.420229061081</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="G10" t="n">
         <v>1149.350535904519</v>
@@ -4959,22 +4959,22 @@
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
@@ -4998,7 +4998,7 @@
         <v>1024.420229061081</v>
       </c>
       <c r="Y10" t="n">
-        <v>1024.420229061081</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C11" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D11" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E11" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G11" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H11" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I11" t="n">
         <v>81.36</v>
@@ -5038,16 +5038,16 @@
         <v>1182.375479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>2089.404973955146</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2600.253802684082</v>
+        <v>1693.224308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>3213.474122458845</v>
+        <v>2306.444627889222</v>
       </c>
       <c r="O11" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P11" t="n">
         <v>3629.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T11" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U11" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V11" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W11" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X11" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y11" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="12">
@@ -5120,13 +5120,13 @@
         <v>1341.904675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O12" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P12" t="n">
         <v>2600.013000882351</v>
@@ -5202,16 +5202,16 @@
         <v>425.5789893823512</v>
       </c>
       <c r="N13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R13" t="n">
         <v>81.36</v>
@@ -5248,46 +5248,46 @@
         <v>1229.164925096351</v>
       </c>
       <c r="C14" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D14" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E14" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F14" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G14" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H14" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I14" t="n">
         <v>81.36</v>
       </c>
       <c r="J14" t="n">
-        <v>374.1524465568547</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>1083.858812904723</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1990.888307474345</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M14" t="n">
-        <v>2501.73713620328</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N14" t="n">
-        <v>3114.957455978044</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O14" t="n">
-        <v>4068</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P14" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>4068</v>
@@ -5448,7 +5448,7 @@
         <v>425.5789893823512</v>
       </c>
       <c r="Q16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R16" t="n">
         <v>81.36</v>
@@ -5482,34 +5482,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D17" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E17" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F17" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G17" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H17" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I17" t="n">
         <v>81.36</v>
       </c>
       <c r="J17" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>690.7012485145707</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L17" t="n">
         <v>690.7012485145707</v>
@@ -5530,28 +5530,28 @@
         <v>4068</v>
       </c>
       <c r="R17" t="n">
-        <v>4041.860001183541</v>
+        <v>4036.311321832915</v>
       </c>
       <c r="S17" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T17" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U17" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V17" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W17" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X17" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y17" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="18">
@@ -5588,19 +5588,19 @@
         <v>435.8613981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L18" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M18" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O18" t="n">
-        <v>2264.733656412845</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P18" t="n">
         <v>2600.013000882351</v>
@@ -5743,22 +5743,22 @@
         <v>81.36</v>
       </c>
       <c r="J20" t="n">
-        <v>446.402180233122</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1156.10854658099</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>2063.138041150613</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M20" t="n">
-        <v>2063.138041150613</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N20" t="n">
-        <v>2676.358360925376</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O20" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P20" t="n">
         <v>3629.400904947332</v>
@@ -5980,25 +5980,25 @@
         <v>81.36</v>
       </c>
       <c r="J23" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>791.0663663478683</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1698.095860917491</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M23" t="n">
-        <v>2208.944689646426</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N23" t="n">
-        <v>2822.165009421189</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O23" t="n">
-        <v>3206.412036092893</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P23" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>4068</v>
@@ -6007,19 +6007,19 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S23" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T23" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U23" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W23" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X23" t="n">
         <v>1772.421039319847</v>
@@ -6059,13 +6059,13 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J24" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K24" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L24" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M24" t="n">
         <v>1446.910920121557</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C26" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D26" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E26" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F26" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G26" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H26" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I26" t="n">
         <v>81.36</v>
@@ -6220,19 +6220,19 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>472.6691130376557</v>
+        <v>645.2597178520556</v>
       </c>
       <c r="L26" t="n">
-        <v>690.7012485145707</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M26" t="n">
-        <v>1201.550077243506</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N26" t="n">
-        <v>1814.770397018269</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O26" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>3629.400904947332</v>
@@ -6262,7 +6262,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y26" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6302,16 +6302,16 @@
         <v>847.8042142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2264.733656412845</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P27" t="n">
         <v>2600.013000882351</v>
@@ -6396,7 +6396,7 @@
         <v>425.5789893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R28" t="n">
         <v>81.36</v>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C29" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D29" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E29" t="n">
         <v>628.48793908945</v>
@@ -6457,19 +6457,19 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>690.7012485145707</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>1201.550077243506</v>
+        <v>1693.224308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>1814.770397018269</v>
+        <v>2306.444627889222</v>
       </c>
       <c r="O29" t="n">
-        <v>2767.812941040225</v>
+        <v>3259.487171911179</v>
       </c>
       <c r="P29" t="n">
         <v>3629.400904947332</v>
@@ -6478,28 +6478,28 @@
         <v>4068</v>
       </c>
       <c r="R29" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W29" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X29" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y29" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="30">
@@ -6630,10 +6630,10 @@
         <v>425.5789893823512</v>
       </c>
       <c r="P31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R31" t="n">
         <v>81.36</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C32" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D32" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E32" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F32" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G32" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H32" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I32" t="n">
         <v>81.36</v>
@@ -6694,19 +6694,19 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>1182.375479385524</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="L32" t="n">
-        <v>2089.404973955146</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M32" t="n">
-        <v>2600.253802684082</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N32" t="n">
-        <v>3213.474122458845</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O32" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P32" t="n">
         <v>3629.400904947332</v>
@@ -6724,19 +6724,19 @@
         <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V32" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W32" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X32" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y32" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="33">
@@ -6770,22 +6770,22 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K33" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L33" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P33" t="n">
         <v>2600.013000882351</v>
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>303.5506791955609</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C34" t="n">
-        <v>255.3433593490511</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D34" t="n">
-        <v>194.1956643434395</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E34" t="n">
-        <v>137.6492958212611</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F34" t="n">
-        <v>87.76762312657232</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G34" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H34" t="n">
+        <v>189.862369793817</v>
+      </c>
+      <c r="I34" t="n">
+        <v>237.7452487298999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="K34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="L34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="M34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="N34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="O34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="P34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="R34" t="n">
         <v>81.36</v>
       </c>
-      <c r="I34" t="n">
-        <v>129.2428789360829</v>
-      </c>
-      <c r="J34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="K34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="L34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="M34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="N34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="O34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="P34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="R34" t="n">
-        <v>317.0766195885342</v>
-      </c>
       <c r="S34" t="n">
-        <v>317.0766195885342</v>
+        <v>81.36</v>
       </c>
       <c r="T34" t="n">
-        <v>331.9022987473391</v>
+        <v>96.18567915880486</v>
       </c>
       <c r="U34" t="n">
-        <v>405.2034913856257</v>
+        <v>169.4868717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>430.7748842715717</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>429.3882076668144</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X34" t="n">
-        <v>429.3882076668144</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y34" t="n">
-        <v>366.2918916572565</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="35">
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
         <v>103.3156148520479</v>
@@ -6931,22 +6931,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1500.287941766591</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N35" t="n">
-        <v>1797.400904947332</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6961,19 +6961,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D36" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E36" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F36" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G36" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7037,22 +7037,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>629.7009667234867</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>513.8211415197422</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7165,19 +7165,19 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>137.1709049473328</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K38" t="n">
+        <v>179.7320762183977</v>
+      </c>
+      <c r="L38" t="n">
+        <v>179.7320762183977</v>
+      </c>
+      <c r="M38" t="n">
         <v>690.5809049473327</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1243.990904947333</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="O38" t="n">
         <v>1797.400904947332</v>
@@ -7189,7 +7189,7 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
         <v>2085.68327354774</v>
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J40" t="n">
         <v>1860.696627021627</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7405,49 +7405,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M41" t="n">
-        <v>989.4391130376558</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1542.849113037656</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O41" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F42" t="n">
         <v>44.72</v>
@@ -7508,25 +7508,25 @@
         <v>647.3506049216877</v>
       </c>
       <c r="S42" t="n">
-        <v>466.2983195781991</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T42" t="n">
-        <v>410.3813850150538</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U42" t="n">
-        <v>359.6638499037541</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V42" t="n">
-        <v>294.5015598113094</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W42" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
         <v>267.972474045883</v>
@@ -7639,16 +7639,16 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>179.7320762183974</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>733.1420762183974</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L44" t="n">
-        <v>1286.552076218397</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
         <v>1797.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>409.4673863086053</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
         <v>44.72</v>
@@ -7745,25 +7745,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>404.4874506895348</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O8" t="n">
         <v>455.2478695740924</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,10 +8690,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>490.3759326937771</v>
+        <v>536.2764687165196</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>330.7929522621153</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8930,10 +8930,10 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>615.4962106207786</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9386,16 +9386,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>403.772481228042</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
         <v>1096.663422488788</v>
@@ -9404,7 +9404,7 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>458.3761793434905</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P23" t="n">
         <v>870.5779326741233</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>174.3339442569695</v>
       </c>
       <c r="L26" t="n">
-        <v>220.2344802797121</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9878,7 +9878,7 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>220.2344802797121</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10115,7 +10115,7 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P29" t="n">
-        <v>870.5779326741233</v>
+        <v>373.9372954307356</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,10 +10337,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="L32" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,10 +10349,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10574,16 +10574,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>777.3630622928066</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
@@ -10592,7 +10592,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>313.9750954005603</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,22 +10808,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>128.4277587171436</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>313.9750954005603</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>171.4188408091281</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22715,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59117064605573</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.591170646055978</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23417,7 +23417,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>5.408275783157251</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
         <v>415.445564079015</v>
@@ -23429,7 +23429,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23663,10 +23663,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R16" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>137.3734797028554</v>
@@ -24611,10 +24611,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24845,13 +24845,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -25040,22 +25040,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G34" t="n">
-        <v>17.47145204784206</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25109,7 +25109,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="35">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9356705.662291305</v>
+        <v>9356705.662291303</v>
       </c>
     </row>
     <row r="11">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12425634.43776003</v>
+        <v>12425634.43776002</v>
       </c>
     </row>
     <row r="14">
@@ -26284,7 +26284,7 @@
         <v>1069470.752232171</v>
       </c>
       <c r="G2" t="n">
-        <v>1069470.75223217</v>
+        <v>1069470.752232171</v>
       </c>
       <c r="H2" t="n">
         <v>1069470.75223217</v>
@@ -26293,19 +26293,19 @@
         <v>1069470.75223217</v>
       </c>
       <c r="J2" t="n">
-        <v>1069470.75223217</v>
+        <v>1069470.752232171</v>
       </c>
       <c r="K2" t="n">
         <v>1069470.75223217</v>
       </c>
       <c r="L2" t="n">
-        <v>1069470.752232171</v>
+        <v>1069470.75223217</v>
       </c>
       <c r="M2" t="n">
         <v>1133439.336299335</v>
       </c>
       <c r="N2" t="n">
-        <v>1133439.336299336</v>
+        <v>1133439.336299335</v>
       </c>
       <c r="O2" t="n">
         <v>1133439.336299335</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.2900507811</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121192</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464518</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>369935.2421138707</v>
+        <v>368419.3864255551</v>
       </c>
       <c r="C6" t="n">
-        <v>507513.2222476852</v>
+        <v>505997.3665593694</v>
       </c>
       <c r="D6" t="n">
-        <v>509573.9941600013</v>
+        <v>508058.138471685</v>
       </c>
       <c r="E6" t="n">
-        <v>140404.9377203088</v>
+        <v>138068.2298086106</v>
       </c>
       <c r="F6" t="n">
-        <v>544322.4884839392</v>
+        <v>541985.7805722415</v>
       </c>
       <c r="G6" t="n">
-        <v>545778.045093087</v>
+        <v>543441.3371813898</v>
       </c>
       <c r="H6" t="n">
-        <v>547235.6219317487</v>
+        <v>544898.9140200508</v>
       </c>
       <c r="I6" t="n">
-        <v>548695.233571335</v>
+        <v>546358.5256596372</v>
       </c>
       <c r="J6" t="n">
-        <v>234636.8947742279</v>
+        <v>232300.1868625307</v>
       </c>
       <c r="K6" t="n">
-        <v>551620.6204974158</v>
+        <v>549283.9125857181</v>
       </c>
       <c r="L6" t="n">
-        <v>553086.4258962336</v>
+        <v>550749.7179845353</v>
       </c>
       <c r="M6" t="n">
-        <v>381305.2617572342</v>
+        <v>379563.4119441265</v>
       </c>
       <c r="N6" t="n">
-        <v>544518.1587920884</v>
+        <v>542776.3089789797</v>
       </c>
       <c r="O6" t="n">
-        <v>366485.898049826</v>
+        <v>364744.0482367183</v>
       </c>
       <c r="P6" t="n">
-        <v>548456.5009008362</v>
+        <v>546714.6510877283</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27002,13 +27002,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>125</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>225</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -27042,16 +27042,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>-0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>315.9333609904177</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27563,10 +27563,10 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>33.78964074244533</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27600,7 +27600,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27612,10 +27612,10 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>112.9499176813881</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>236.2044222554369</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I5" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27840,7 +27840,7 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>396.7491155350068</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>294.764305776378</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>162.2737972923793</v>
+        <v>213.3372327421372</v>
       </c>
       <c r="S9" t="n">
         <v>81.5639999646113</v>
@@ -28046,10 +28046,10 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>271.5158434500661</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28080,7 +28080,7 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>371.2361019763158</v>
+        <v>258.7014548257782</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>225</v>
       </c>
       <c r="I11" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>225</v>
       </c>
       <c r="S11" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="T11" t="n">
         <v>225</v>
@@ -28256,7 +28256,7 @@
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28384,7 +28384,7 @@
         <v>225</v>
       </c>
       <c r="C14" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="D14" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>225</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28639,7 +28639,7 @@
         <v>225</v>
       </c>
       <c r="I17" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="S17" t="n">
         <v>225</v>
@@ -28724,7 +28724,7 @@
         <v>225</v>
       </c>
       <c r="K18" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="L18" t="n">
         <v>225</v>
@@ -28739,7 +28739,7 @@
         <v>225</v>
       </c>
       <c r="P18" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q18" t="n">
         <v>225</v>
@@ -29143,7 +29143,7 @@
         <v>225</v>
       </c>
       <c r="S23" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="T23" t="n">
         <v>225</v>
@@ -29158,7 +29158,7 @@
         <v>225</v>
       </c>
       <c r="X23" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="n">
         <v>225</v>
@@ -29195,7 +29195,7 @@
         <v>225</v>
       </c>
       <c r="J24" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K24" t="n">
         <v>225</v>
@@ -29204,7 +29204,7 @@
         <v>225</v>
       </c>
       <c r="M24" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N24" t="n">
         <v>225</v>
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>225</v>
       </c>
       <c r="Y26" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27">
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29575,7 +29575,7 @@
         <v>225</v>
       </c>
       <c r="E29" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="F29" t="n">
         <v>225</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S29" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>225</v>
       </c>
       <c r="I32" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29860,7 +29860,7 @@
         <v>225</v>
       </c>
       <c r="U32" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="V32" t="n">
         <v>225</v>
@@ -29906,7 +29906,7 @@
         <v>225</v>
       </c>
       <c r="J33" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K33" t="n">
         <v>225</v>
@@ -29924,7 +29924,7 @@
         <v>225</v>
       </c>
       <c r="P33" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q33" t="n">
         <v>225</v>
@@ -30055,7 +30055,7 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
@@ -30097,7 +30097,7 @@
         <v>350</v>
       </c>
       <c r="U35" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V35" t="n">
         <v>350</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30137,10 +30137,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30173,7 +30173,7 @@
         <v>350</v>
       </c>
       <c r="T36" t="n">
-        <v>154.4486233659061</v>
+        <v>350</v>
       </c>
       <c r="U36" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30365,10 +30365,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30416,7 +30416,7 @@
         <v>350</v>
       </c>
       <c r="V39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="W39" t="n">
         <v>350</v>
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30605,7 +30605,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124345</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
@@ -30644,7 +30644,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30757,7 +30757,7 @@
         <v>350</v>
       </c>
       <c r="D44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="E44" t="n">
         <v>350</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30881,10 +30881,10 @@
         <v>350</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U45" t="n">
         <v>350</v>
@@ -34886,7 +34886,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34898,10 +34898,10 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>77.68096884548036</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>85.24603098097896</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -35126,7 +35126,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>122.3662595672648</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>84.73973927012027</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35229,7 +35229,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="O8" t="n">
         <v>385</v>
@@ -35366,7 +35366,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>126.1922291347857</v>
+        <v>13.65758198424814</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35460,7 +35460,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,10 +35469,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>420.1280631196846</v>
+        <v>466.0285991424272</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35542,7 +35542,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>295.7499460170249</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35709,10 +35709,10 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>615.4962106207786</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -36010,7 +36010,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>499.091375348687</v>
@@ -36025,7 +36025,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q18" t="n">
         <v>51.92073490952041</v>
@@ -36165,16 +36165,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>368.7294749829516</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
         <v>619.4144644189528</v>
@@ -36183,7 +36183,7 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,13 +36417,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>388.1283097693981</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P23" t="n">
         <v>870.2908726334418</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J24" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K24" t="n">
         <v>416.1038546407913</v>
@@ -36490,7 +36490,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N24" t="n">
         <v>359.6265501086548</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>174.3339442569695</v>
       </c>
       <c r="L26" t="n">
-        <v>220.2344802797121</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36657,7 +36657,7 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>293.2082466075261</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
-        <v>220.2344802797121</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36894,7 +36894,7 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P29" t="n">
-        <v>870.2908726334418</v>
+        <v>373.6502353900542</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -37116,10 +37116,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230996</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="L32" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37128,10 +37128,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37192,7 +37192,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K33" t="n">
         <v>416.1038546407913</v>
@@ -37210,7 +37210,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>51.92073490952041</v>
@@ -37353,16 +37353,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>141.1524110730749</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,22 +37587,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>93.38475247205329</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>141.1524110730749</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>136.3758345640378</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
